--- a/Analysis/Prompt_Ablation/prompt_ablation_posthoc_tests.xlsx
+++ b/Analysis/Prompt_Ablation/prompt_ablation_posthoc_tests.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O4"/>
+  <dimension ref="A1:O7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -520,13 +520,13 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>520.5</v>
+        <v>526.5</v>
       </c>
       <c r="G2" t="n">
-        <v>6.282327479267287e-05</v>
+        <v>7.34278993374151e-05</v>
       </c>
       <c r="H2" t="n">
-        <v>0.5562659846547314</v>
+        <v>0.551150895140665</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -537,7 +537,7 @@
         <v>68</v>
       </c>
       <c r="K2" t="n">
-        <v>0.04817882971729125</v>
+        <v>0.04904667981591058</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>
@@ -548,7 +548,7 @@
         <v>195</v>
       </c>
       <c r="N2" t="n">
-        <v>0.0001884698243780186</v>
+        <v>0.0002202836980122453</v>
       </c>
       <c r="O2" t="b">
         <v>1</v>
@@ -581,13 +581,13 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2071</v>
+        <v>508.5</v>
       </c>
       <c r="G3" t="n">
-        <v>0.004625170486324907</v>
+        <v>0.002625479855890568</v>
       </c>
       <c r="H3" t="n">
-        <v>0.3090909090909091</v>
+        <v>0.4442622950819672</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -595,10 +595,10 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>109</v>
+        <v>60</v>
       </c>
       <c r="K3" t="n">
-        <v>0.02406311637080868</v>
+        <v>0.03702827087442472</v>
       </c>
       <c r="L3" t="inlineStr">
         <is>
@@ -609,7 +609,7 @@
         <v>195</v>
       </c>
       <c r="N3" t="n">
-        <v>0.009250340972649814</v>
+        <v>0.005250959711781137</v>
       </c>
       <c r="O3" t="b">
         <v>1</v>
@@ -642,24 +642,24 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1906.5</v>
+        <v>361</v>
       </c>
       <c r="G4" t="n">
-        <v>0.06090764123510683</v>
+        <v>0.07588327712701348</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.2139764996907854</v>
+        <v>-0.3024154589371981</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>small</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="J4" t="n">
-        <v>98</v>
+        <v>45</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.01964497041420118</v>
+        <v>-0.01094017094017094</v>
       </c>
       <c r="L4" t="inlineStr">
         <is>
@@ -670,9 +670,192 @@
         <v>195</v>
       </c>
       <c r="N4" t="n">
-        <v>0.06090764123510683</v>
+        <v>0.07588327712701348</v>
       </c>
       <c r="O4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>AD</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>qwen</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>kendall_tau</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>control</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>cot_scaffold</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
+        <v>6036.5</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.0004319605796425415</v>
+      </c>
+      <c r="H5" t="n">
+        <v>-0.2982853821563499</v>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>small</t>
+        </is>
+      </c>
+      <c r="J5" t="n">
+        <v>185</v>
+      </c>
+      <c r="K5" t="n">
+        <v>-0.1604733727810651</v>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>small</t>
+        </is>
+      </c>
+      <c r="M5" t="n">
+        <v>195</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0.001295881738927624</v>
+      </c>
+      <c r="O5" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>AD</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>qwen</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>kendall_tau</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>cot_scaffold</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>no_anchors</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
+        <v>7325</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.03694021336660368</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.1753911966677924</v>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>small</t>
+        </is>
+      </c>
+      <c r="J6" t="n">
+        <v>188</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0.1359105851413544</v>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>negligible</t>
+        </is>
+      </c>
+      <c r="M6" t="n">
+        <v>195</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0.07388042673320735</v>
+      </c>
+      <c r="O6" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>AD</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>qwen</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>kendall_tau</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>control</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>no_anchors</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
+        <v>7633</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.7210640201653558</v>
+      </c>
+      <c r="H7" t="n">
+        <v>-0.03091474639751159</v>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>negligible</t>
+        </is>
+      </c>
+      <c r="J7" t="n">
+        <v>177</v>
+      </c>
+      <c r="K7" t="n">
+        <v>-0.007337278106508876</v>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>negligible</t>
+        </is>
+      </c>
+      <c r="M7" t="n">
+        <v>195</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0.7210640201653558</v>
+      </c>
+      <c r="O7" t="b">
         <v>0</v>
       </c>
     </row>
